--- a/scripts/ItemCodeList/CodeList.xlsx
+++ b/scripts/ItemCodeList/CodeList.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Private\Claude Code\NextJSTryAgain\NextJSTryAgain\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Private\Claude Code\NextJSTryAgain\NextJSTryAgain\scripts\ItemCodeList\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2FD09AB-6F07-4534-BAF8-D42C4472604B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{574B66FF-5581-4CE2-8DB3-95DF3BDB0D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="20610" windowHeight="11040" xr2:uid="{5731B701-3ED4-4C40-9287-7AD159B2809E}"/>
   </bookViews>
